--- a/outputs/daily/hr_rankings_2026-08-22_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22_remaining.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -16920,7 +16920,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -17200,7 +17200,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -18576,7 +18576,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -19692,7 +19692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -20812,7 +20812,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -21092,7 +21092,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -22492,7 +22492,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -24452,7 +24452,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -27224,7 +27224,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -28904,7 +28904,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -29464,7 +29464,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -30584,7 +30584,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -31144,7 +31144,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -31424,7 +31424,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -31984,7 +31984,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -32264,7 +32264,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -32800,7 +32800,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -34448,7 +34448,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -34728,7 +34728,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -35008,7 +35008,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -35848,7 +35848,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -36128,7 +36128,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -36408,7 +36408,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -36688,7 +36688,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -36968,7 +36968,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -38088,7 +38088,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -40300,7 +40300,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -40580,7 +40580,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -40860,7 +40860,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -41676,7 +41676,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -41956,7 +41956,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -42236,7 +42236,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -42796,7 +42796,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -43076,7 +43076,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -44196,7 +44196,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -45032,7 +45032,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -45312,7 +45312,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -45592,7 +45592,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -47268,7 +47268,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -48108,7 +48108,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -48388,7 +48388,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -48948,7 +48948,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -49228,7 +49228,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -49508,7 +49508,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -50068,7 +50068,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -50628,7 +50628,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -50908,7 +50908,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -51188,7 +51188,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -51468,7 +51468,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -51748,7 +51748,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -53708,7 +53708,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -54268,7 +54268,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -54548,7 +54548,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -55388,7 +55388,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -56554,7 +56554,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -56834,7 +56834,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -57954,7 +57954,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -58514,7 +58514,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -59074,7 +59074,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -59354,7 +59354,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -59910,7 +59910,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -60190,7 +60190,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -60470,7 +60470,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -60750,7 +60750,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -61030,7 +61030,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-22_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22_remaining.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -11932,7 +11932,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -14444,7 +14444,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -17842,7 +17842,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -18402,7 +18402,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -20082,7 +20082,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -20918,7 +20918,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -21478,7 +21478,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
